--- a/dataset_info.xlsx
+++ b/dataset_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\FFL_TBMA\experiments_final_corrected\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\tbma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7700DB-8C8D-4021-B966-EC307D467DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF01173A-1B2D-4BDE-8910-1B53E1A19BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,8 +1200,8 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>1</v>
+      <c r="G2" s="1">
+        <v>0</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1226,8 +1226,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="G3" s="1">
+        <v>0</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1252,8 +1252,8 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>1</v>
+      <c r="G4" s="1">
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1281,8 +1281,8 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="G5" s="1">
+        <v>0</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1307,8 +1307,8 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="G6" s="1">
+        <v>0</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1336,8 +1336,8 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>1</v>
+      <c r="G7" s="1">
+        <v>0</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1362,8 +1362,8 @@
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8">
-        <v>1</v>
+      <c r="G8" s="1">
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1388,8 +1388,8 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>1</v>
+      <c r="G9" s="1">
+        <v>0</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1443,8 +1443,8 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11">
-        <v>1</v>
+      <c r="G11" s="1">
+        <v>0</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1469,8 +1469,8 @@
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12">
-        <v>1</v>
+      <c r="G12" s="1">
+        <v>0</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1576,8 +1576,8 @@
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16">
-        <v>1</v>
+      <c r="G16" s="1">
+        <v>0</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1683,8 +1683,8 @@
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20">
-        <v>1</v>
+      <c r="G20" s="1">
+        <v>0</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1787,8 +1787,8 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24">
-        <v>1</v>
+      <c r="G24" s="1">
+        <v>0</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2411,8 +2411,8 @@
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48">
-        <v>1</v>
+      <c r="G48" s="1">
+        <v>0</v>
       </c>
       <c r="H48">
         <v>1</v>

--- a/dataset_info.xlsx
+++ b/dataset_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\tbma\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\FFL_TBMA\experiments_final_corrected\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF01173A-1B2D-4BDE-8910-1B53E1A19BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7700DB-8C8D-4021-B966-EC307D467DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,8 +1200,8 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1226,8 +1226,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" s="1">
-        <v>0</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1252,8 +1252,8 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" s="1">
-        <v>0</v>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1281,8 +1281,8 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
+      <c r="G5">
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1307,8 +1307,8 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1336,8 +1336,8 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
+      <c r="G7">
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1362,8 +1362,8 @@
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1388,8 +1388,8 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
+      <c r="G9">
+        <v>1</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1443,8 +1443,8 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
+      <c r="G11">
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1469,8 +1469,8 @@
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1576,8 +1576,8 @@
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
+      <c r="G16">
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1683,8 +1683,8 @@
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" s="1">
-        <v>0</v>
+      <c r="G20">
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1787,8 +1787,8 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" s="1">
-        <v>0</v>
+      <c r="G24">
+        <v>1</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2411,8 +2411,8 @@
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48" s="1">
-        <v>0</v>
+      <c r="G48">
+        <v>1</v>
       </c>
       <c r="H48">
         <v>1</v>

--- a/dataset_info.xlsx
+++ b/dataset_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\FFL_TBMA\experiments_final_corrected\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oguzh\My_Research\tbma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7700DB-8C8D-4021-B966-EC307D467DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E6BD6C-EBC5-4479-BCD1-30257C3F3E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="repo_data" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="129">
   <si>
     <t>Dataset</t>
   </si>
@@ -56,15 +56,6 @@
     <t>evaluate</t>
   </si>
   <si>
-    <t>test_period</t>
-  </si>
-  <si>
-    <t>test_period_sensitivity</t>
-  </si>
-  <si>
-    <t>external_norm_features</t>
-  </si>
-  <si>
     <t>Tourism Yearly</t>
   </si>
   <si>
@@ -92,24 +83,12 @@
     <t>tourism_monthly_dataset.tsf</t>
   </si>
   <si>
-    <t>M5 Daily</t>
-  </si>
-  <si>
-    <t>m5_daily</t>
-  </si>
-  <si>
     <t>m5_dataset.tsf</t>
   </si>
   <si>
     <t>M1 Monthly</t>
   </si>
   <si>
-    <t>m1_monthly</t>
-  </si>
-  <si>
-    <t>m1_monthly_dataset.tsf</t>
-  </si>
-  <si>
     <t>M1 Quarterly</t>
   </si>
   <si>
@@ -131,12 +110,6 @@
     <t>M3 Monthly</t>
   </si>
   <si>
-    <t>m3_monthly</t>
-  </si>
-  <si>
-    <t>m3_monthly_dataset.tsf</t>
-  </si>
-  <si>
     <t>M3 Other</t>
   </si>
   <si>
@@ -167,102 +140,36 @@
     <t>M4 Hourly</t>
   </si>
   <si>
-    <t>m4_hourly</t>
-  </si>
-  <si>
-    <t>m4_hourly_dataset.tsf</t>
-  </si>
-  <si>
     <t>M4 Weekly</t>
   </si>
   <si>
-    <t>m4_weekly</t>
-  </si>
-  <si>
-    <t>m4_weekly_dataset.tsf</t>
-  </si>
-  <si>
     <t>NN5 Daily</t>
   </si>
   <si>
-    <t>nn5_daily</t>
-  </si>
-  <si>
-    <t>nn5_daily_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>NN5 Weekly</t>
   </si>
   <si>
-    <t>nn5_weekly</t>
-  </si>
-  <si>
-    <t>nn5_weekly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Saugeen River Flow</t>
   </si>
   <si>
-    <t>saugeenday</t>
-  </si>
-  <si>
-    <t>saugeenday_dataset.tsf</t>
-  </si>
-  <si>
     <t>Solar Weekly</t>
   </si>
   <si>
-    <t>solar_weekly</t>
-  </si>
-  <si>
-    <t>solar_weekly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Sunspot</t>
   </si>
   <si>
-    <t>sunspot</t>
-  </si>
-  <si>
-    <t>sunspot_dataset.tsf</t>
-  </si>
-  <si>
     <t>Traffic Weekly</t>
   </si>
   <si>
-    <t>traffic_weekly</t>
-  </si>
-  <si>
-    <t>traffic_weekly_dataset.tsf</t>
-  </si>
-  <si>
     <t>US Births</t>
   </si>
   <si>
-    <t>us_births</t>
-  </si>
-  <si>
-    <t>us_births_dataset.tsf</t>
-  </si>
-  <si>
     <t>Bitcoin</t>
   </si>
   <si>
-    <t>bitcoin</t>
-  </si>
-  <si>
-    <t>bitcoin_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>COVID Deaths</t>
   </si>
   <si>
-    <t>covid_deaths</t>
-  </si>
-  <si>
-    <t>covid_deaths_dataset.tsf</t>
-  </si>
-  <si>
     <t>FREDMD</t>
   </si>
   <si>
@@ -275,201 +182,60 @@
     <t>Hospital</t>
   </si>
   <si>
-    <t>hospital</t>
-  </si>
-  <si>
-    <t>hospital_dataset.tsf</t>
-  </si>
-  <si>
     <t>M4 Daily</t>
   </si>
   <si>
-    <t>m4_daily</t>
-  </si>
-  <si>
-    <t>m4_daily_dataset.tsf</t>
-  </si>
-  <si>
     <t>M4 Quarterly</t>
   </si>
   <si>
-    <t>m4_quarterly</t>
-  </si>
-  <si>
-    <t>m4_quarterly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Traffic Hourly</t>
   </si>
   <si>
-    <t>traffic_hourly</t>
-  </si>
-  <si>
-    <t>traffic_hourly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Aus. Elecdemand</t>
   </si>
   <si>
-    <t>australian_electricity_demand</t>
-  </si>
-  <si>
-    <t>australian_electricity_demand_dataset.tsf</t>
-  </si>
-  <si>
     <t>Pedestrians</t>
   </si>
   <si>
-    <t>pedestrian_counts</t>
-  </si>
-  <si>
-    <t>pedestrian_counts_dataset.tsf</t>
-  </si>
-  <si>
     <t>Rideshare</t>
   </si>
   <si>
-    <t>rideshare</t>
-  </si>
-  <si>
-    <t>rideshare_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>Solar 10 Mins</t>
   </si>
   <si>
-    <t>solar_10_minutes</t>
-  </si>
-  <si>
-    <t>solar_10_minutes_dataset.tsf</t>
-  </si>
-  <si>
     <t>Temp. Rain</t>
   </si>
   <si>
-    <t>temperature_rain</t>
-  </si>
-  <si>
-    <t>temperature_rain_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>Carparts</t>
   </si>
   <si>
-    <t>car_parts</t>
-  </si>
-  <si>
-    <t>car_parts_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>Electricity Hourly</t>
   </si>
   <si>
-    <t>electricity_hourly</t>
-  </si>
-  <si>
-    <t>electricity_hourly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Electricity Weekly</t>
   </si>
   <si>
-    <t>electricity_weekly</t>
-  </si>
-  <si>
-    <t>electricity_weekly_dataset.tsf</t>
-  </si>
-  <si>
     <t>KDD</t>
   </si>
   <si>
-    <t>kdd_cup_2018</t>
-  </si>
-  <si>
-    <t>kdd_cup_2018_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>Kaggle Daily</t>
   </si>
   <si>
-    <t>kaggle_daily</t>
-  </si>
-  <si>
-    <t>kaggle_web_traffic_dataset_1000_without_missing_values.tsf</t>
-  </si>
-  <si>
-    <t>Kaggle Daily with Cov</t>
-  </si>
-  <si>
-    <t>kaggle_daily_with_cov</t>
-  </si>
-  <si>
-    <t>kaggle_1000_with_date_covariates.tsf</t>
-  </si>
-  <si>
-    <t>Wikipedia web traffic</t>
-  </si>
-  <si>
-    <t>wikipedia_web_traffic</t>
-  </si>
-  <si>
     <t>kaggle_web_traffic_1000_dataset.tsf</t>
   </si>
   <si>
-    <t>Kaggle Weekly repo</t>
-  </si>
-  <si>
-    <t>kaggle_web_traffic_weekly</t>
-  </si>
-  <si>
-    <t>kaggle_web_traffic_weekly_dataset.tsf</t>
-  </si>
-  <si>
-    <t>Kaggle Daily repo</t>
-  </si>
-  <si>
-    <t>kaggle_web_traffic</t>
-  </si>
-  <si>
-    <t>kaggle_web_traffic_dataset.tsf</t>
-  </si>
-  <si>
     <t>M4 Yearly</t>
   </si>
   <si>
-    <t>m4_yearly</t>
-  </si>
-  <si>
-    <t>m4_yearly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Vehicle Trips</t>
   </si>
   <si>
-    <t>vehicle_trips</t>
-  </si>
-  <si>
-    <t>vehicle_trips_dataset_without_missing_values.tsf</t>
-  </si>
-  <si>
     <t>M4 Monthly</t>
   </si>
   <si>
-    <t>m4_monthly</t>
-  </si>
-  <si>
-    <t>m4_monthly_dataset.tsf</t>
-  </si>
-  <si>
     <t>Dominick</t>
   </si>
   <si>
-    <t>dominick</t>
-  </si>
-  <si>
-    <t>dominick_dataset.tsf</t>
-  </si>
-  <si>
     <t>kaggle</t>
   </si>
   <si>
@@ -479,28 +245,7 @@
     <t>CIF 2016</t>
   </si>
   <si>
-    <t>cif_2016</t>
-  </si>
-  <si>
-    <t>cif_2016_dataset.tsf</t>
-  </si>
-  <si>
     <t>Weather</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>Wind Farms</t>
-  </si>
-  <si>
-    <t>wind_farms</t>
-  </si>
-  <si>
-    <t>London Smart Meter</t>
-  </si>
-  <si>
-    <t>london_smart_meter</t>
   </si>
   <si>
     <t>favourita</t>
@@ -686,7 +431,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -695,14 +440,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF729FCF"/>
-        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -718,13 +457,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -734,6 +468,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1136,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultColWidth="12.26953125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
@@ -1146,7 +881,7 @@
     <col min="11" max="11" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1171,25 +906,16 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1207,20 +933,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>5</v>
       </c>
       <c r="F3">
@@ -1233,15 +959,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>24</v>
@@ -1258,25 +984,22 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
       <c r="D5">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1288,21 +1011,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
       <c r="D6">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1313,11 +1036,8 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1331,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1343,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1354,10 +1074,10 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1369,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1380,10 +1100,10 @@
         <v>34</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1395,21 +1115,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1420,1050 +1140,8 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13">
-        <v>48</v>
-      </c>
-      <c r="E13">
-        <v>210</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
-      <c r="E14">
-        <v>65</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15">
-        <v>56</v>
-      </c>
-      <c r="E15">
-        <v>9</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>65</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17">
-        <v>30</v>
-      </c>
-      <c r="E17">
-        <v>9</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19">
-        <v>30</v>
-      </c>
-      <c r="E19">
-        <v>9</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>65</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21">
-        <v>30</v>
-      </c>
-      <c r="E21">
-        <v>9</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22">
-        <v>30</v>
-      </c>
-      <c r="E22">
-        <v>9</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23">
-        <v>30</v>
-      </c>
-      <c r="E23">
-        <v>9</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24">
-        <v>15</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25">
-        <v>12</v>
-      </c>
-      <c r="E25">
-        <v>15</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26">
-        <v>14</v>
-      </c>
-      <c r="E26">
-        <v>9</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27">
-        <v>8</v>
-      </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28">
-        <v>168</v>
-      </c>
-      <c r="E28">
-        <v>30</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29">
-        <v>336</v>
-      </c>
-      <c r="E29">
-        <v>420</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30">
-        <v>24</v>
-      </c>
-      <c r="E30">
-        <v>210</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31">
-        <v>168</v>
-      </c>
-      <c r="E31">
-        <v>210</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32">
-        <v>1008</v>
-      </c>
-      <c r="E32" s="2">
-        <v>50</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33">
-        <v>30</v>
-      </c>
-      <c r="E33">
-        <v>9</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34">
-        <v>12</v>
-      </c>
-      <c r="E34">
-        <v>15</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>110</v>
-      </c>
-      <c r="B35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35">
-        <v>168</v>
-      </c>
-      <c r="E35">
-        <v>30</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36">
-        <v>8</v>
-      </c>
-      <c r="E36">
-        <v>65</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
-      </c>
-      <c r="C37" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37">
-        <v>168</v>
-      </c>
-      <c r="E37">
-        <v>210</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38">
-        <v>59</v>
-      </c>
-      <c r="E38">
-        <v>10</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39">
-        <v>59</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40">
-        <v>59</v>
-      </c>
-      <c r="E40">
-        <v>10</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>128</v>
-      </c>
-      <c r="B41" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41">
-        <v>8</v>
-      </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>131</v>
-      </c>
-      <c r="B42" t="s">
-        <v>132</v>
-      </c>
-      <c r="C42" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42">
-        <v>8</v>
-      </c>
-      <c r="E42">
-        <v>10</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B43" t="s">
-        <v>135</v>
-      </c>
-      <c r="C43" t="s">
-        <v>136</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43">
-        <v>2</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>137</v>
-      </c>
-      <c r="B44" t="s">
-        <v>138</v>
-      </c>
-      <c r="C44" t="s">
-        <v>139</v>
-      </c>
-      <c r="D44">
-        <v>30</v>
-      </c>
-      <c r="E44">
-        <v>9</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B45" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45">
-        <v>18</v>
-      </c>
-      <c r="E45">
-        <v>15</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" t="s">
-        <v>145</v>
-      </c>
-      <c r="D46">
-        <v>8</v>
-      </c>
-      <c r="E46">
-        <v>10</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>146</v>
-      </c>
-      <c r="B47" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47">
-        <v>59</v>
-      </c>
-      <c r="E47">
-        <v>10</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" t="s">
-        <v>149</v>
-      </c>
-      <c r="C48" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48">
-        <v>12</v>
-      </c>
-      <c r="E48">
-        <v>15</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>151</v>
-      </c>
-      <c r="B49" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49">
-        <v>30</v>
-      </c>
-      <c r="E49">
-        <v>9</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>155</v>
-      </c>
-      <c r="B51" t="s">
-        <v>156</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -2497,90 +1175,90 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +1278,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
-        <v>171</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2608,45 +1286,45 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>177</v>
+        <v>92</v>
       </c>
       <c r="H2" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="I2" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="K2" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="M2" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>4.9379999999999997</v>
@@ -2687,7 +1365,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1.929</v>
@@ -2728,7 +1406,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>1.379</v>
@@ -2769,7 +1447,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>3.1669999999999998</v>
@@ -2810,7 +1488,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1.417</v>
@@ -2851,7 +1529,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>1.091</v>
@@ -2892,7 +1570,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>3.089</v>
@@ -2933,7 +1611,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="B10">
         <v>3.9809999999999999</v>
@@ -2957,24 +1635,24 @@
         <v>3.649</v>
       </c>
       <c r="I10" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>1.417</v>
@@ -3015,7 +1693,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <v>1.1499999999999999</v>
@@ -3056,7 +1734,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>0.58699999999999997</v>
@@ -3097,7 +1775,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>1.1539999999999999</v>
@@ -3138,7 +1816,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>11.606999999999999</v>
@@ -3179,7 +1857,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>3.2530000000000001</v>
@@ -3220,7 +1898,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>3.21</v>
@@ -3261,7 +1939,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>3.306</v>
@@ -3302,7 +1980,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="B19">
         <v>1.2909999999999999</v>
@@ -3343,7 +2021,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>1.857</v>
@@ -3384,7 +2062,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="B21">
         <v>0.58199999999999996</v>
@@ -3425,7 +2103,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="B22">
         <v>4.327</v>
@@ -3466,7 +2144,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0.95699999999999996</v>
@@ -3507,7 +2185,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>1.224</v>
@@ -3548,7 +2226,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="B25">
         <v>1.645</v>
@@ -3589,7 +2267,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="B26">
         <v>0.67700000000000005</v>
@@ -3630,7 +2308,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>1.5209999999999999</v>
@@ -3671,7 +2349,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>0.90300000000000002</v>
@@ -3712,7 +2390,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="B29">
         <v>0.92400000000000004</v>
@@ -3730,30 +2408,30 @@
         <v>0.89</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="I29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="J29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="K29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="L29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="M29" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="B30">
         <v>0.69799999999999995</v>
@@ -3794,7 +2472,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="B31">
         <v>1.4510000000000001</v>
@@ -3827,7 +2505,7 @@
         <v>1.573</v>
       </c>
       <c r="L31" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="M31">
         <v>1.4510000000000001</v>
@@ -3835,7 +2513,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>1.2150000000000001</v>
@@ -3876,7 +2554,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="B33">
         <v>4.5439999999999996</v>
@@ -3917,7 +2595,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="B34">
         <v>1.536</v>
@@ -3958,7 +2636,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="B35">
         <v>0.89700000000000002</v>
@@ -3999,7 +2677,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="B36">
         <v>0.61699999999999999</v>
@@ -4040,7 +2718,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="B37">
         <v>1.9219999999999999</v>
@@ -4081,7 +2759,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B38">
         <v>1.1160000000000001</v>
@@ -4122,7 +2800,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>3.0139999999999998</v>
@@ -4163,7 +2841,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>0.81299999999999994</v>
@@ -4204,7 +2882,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="B41">
         <v>7.7759999999999998</v>
@@ -4245,7 +2923,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B42">
         <v>1.347</v>
@@ -4286,7 +2964,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B43">
         <v>0.128</v>
@@ -4327,7 +3005,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="B44">
         <v>1.4259999999999999</v>
@@ -4368,7 +3046,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="B45">
         <v>4.343</v>
@@ -4423,1820 +3101,1820 @@
   <sheetFormatPr defaultColWidth="12.26953125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08984375" customWidth="1"/>
-    <col min="2" max="2" width="7" style="4" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" style="4" customWidth="1"/>
-    <col min="4" max="5" width="7" style="4" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="7" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9" style="4" customWidth="1"/>
-    <col min="9" max="9" width="7" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="9.26953125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.90625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>183</v>
+      <c r="B1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="4">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1">
         <v>23.08</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>20.16</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>17.41</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="1">
         <v>18.600000000000001</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="1">
         <v>19.46</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="1">
         <v>18.77</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="1">
         <v>20.239999999999998</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="1">
         <v>18.190000000000001</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="1">
         <v>18.7</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="1">
         <v>20.5</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="1">
         <v>21.23</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="1">
         <v>18.95</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="4">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1">
         <v>18.07</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>16.329999999999998</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>16.62</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="1">
         <v>17.41</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>16.59</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="1">
         <v>16.64</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="1">
         <v>17.57</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="1">
         <v>16.420000000000002</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="1">
         <v>16.14</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="1">
         <v>16.73</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="1">
         <v>15.73</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="1">
         <v>19.34</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1">
         <v>17.12</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>15.53</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="1">
         <v>14.82</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="1">
         <v>14.64</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="1">
         <v>15.26</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="1">
         <v>14.85</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="1">
         <v>16.05</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="1">
         <v>15.4</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="1">
         <v>16.079999999999998</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="1">
         <v>16.2</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="1">
         <v>16.27</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="1">
         <v>21.85</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1">
         <v>17.760000000000002</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>16.760000000000002</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>17.37</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="1">
         <v>17</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>18.84</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="1">
         <v>17.13</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="1">
         <v>20.07</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="1">
         <v>17.59</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>17.239999999999998</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>17.03</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="1">
         <v>16.98</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>15.82</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="4">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
         <v>10.9</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>10.220000000000001</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="1">
         <v>9.68</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="1">
         <v>10.24</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="1">
         <v>9.77</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="1">
         <v>11.18</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="1">
         <v>9.9</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="1">
         <v>9.93</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="1">
         <v>9.4700000000000006</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="1">
         <v>9.7200000000000006</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="1">
         <v>13.17</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="4">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
         <v>16.22</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="1">
         <v>13.86</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>13.85</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>14.14</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <v>14.24</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="1">
         <v>15.17</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="1">
         <v>16.41</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="1">
         <v>15.33</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="1">
         <v>15.74</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="1">
         <v>14.76</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="1">
         <v>15.43</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="1">
         <v>17.13</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="4">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
         <v>6.28</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="1">
         <v>4.92</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <v>4.3499999999999996</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="1">
         <v>4.37</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="1">
         <v>4.3499999999999996</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="1">
         <v>5.32</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="1">
         <v>6.74</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="1">
         <v>5.41</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="1">
         <v>5.57</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="1">
         <v>4.97</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="1">
         <v>5.09</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="1">
         <v>5.78</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="4">
+        <v>64</v>
+      </c>
+      <c r="B9" s="1">
         <v>16.399999999999999</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="1">
         <v>14.56</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <v>14.92</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="1">
         <v>15.36</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <v>16.03</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="1">
         <v>14.53</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="1">
         <v>15.28</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>184</v>
+      <c r="I9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="4">
+        <v>51</v>
+      </c>
+      <c r="B10" s="1">
         <v>11.08</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="1">
         <v>10.31</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <v>10.19</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="1">
         <v>10.29</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="1">
         <v>10.52</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="1">
         <v>10.83</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="1">
         <v>10.81</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="1">
         <v>11.09</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="1">
         <v>10.64</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="1">
         <v>10.46</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="1">
         <v>10.75</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="1">
         <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B11" s="4">
+        <v>66</v>
+      </c>
+      <c r="B11" s="1">
         <v>14.38</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="1">
         <v>13.01</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="1">
         <v>12.95</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="1">
         <v>13.52</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <v>13.08</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="1">
         <v>13.73</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="1">
         <v>14.05</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="1">
         <v>14.03</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="1">
         <v>14.29</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="1">
         <v>13.4</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="1">
         <v>15.42</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="1">
         <v>18.37</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="4">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1">
         <v>9.01</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="1">
         <v>7.83</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="1">
         <v>7.3</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="1">
         <v>8.73</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="1">
         <v>7.94</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="1">
         <v>7.43</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="1">
         <v>7.44</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="1">
         <v>8.5399999999999991</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="1">
         <v>7.93</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="1">
         <v>6.81</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="1">
         <v>9.2100000000000009</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="4">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1">
         <v>3.04</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="1">
         <v>3.07</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="1">
         <v>3</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="1">
         <v>3.13</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <v>3.01</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="1">
         <v>3.06</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="1">
         <v>3.47</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="1">
         <v>3.06</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="1">
         <v>5.04</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="1">
         <v>3.2</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="1">
         <v>3.19</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M13" s="1">
         <v>3.55</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="4">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1">
         <v>42.92</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="1">
         <v>42.94</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="1">
         <v>28.1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="1">
         <v>69.510000000000005</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="1">
         <v>35.94</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="1">
         <v>11.67</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="1">
         <v>9.5399999999999991</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="1">
         <v>16.239999999999998</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="1">
         <v>15.06</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="1">
         <v>15.73</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="1">
         <v>12.04</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="1">
         <v>15.72</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1">
         <v>34.1</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="1">
         <v>31.93</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="1">
         <v>33.94</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="1">
         <v>36.520000000000003</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="1">
         <v>33.39</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="1">
         <v>46.92</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="1">
         <v>31.54</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="1">
         <v>33.729999999999997</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="1">
         <v>34.06</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="1">
         <v>30.24</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="1">
         <v>28.8</v>
       </c>
-      <c r="M15" s="4">
+      <c r="M15" s="1">
         <v>34.659999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1">
         <v>27.41</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="1">
         <v>15.37</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="1">
         <v>17.16</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="1">
         <v>15.07</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="1">
         <v>16.579999999999998</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="1">
         <v>15.86</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="1">
         <v>16.53</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="1">
         <v>16.2</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="1">
         <v>15.29</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="1">
         <v>14.45</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="1">
         <v>15.56</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M16" s="1">
         <v>16.97</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
         <v>36.39</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="1">
         <v>19.89</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="1">
         <v>21.2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="1">
         <v>19.02</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="1">
         <v>19.73</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="1">
         <v>21.11</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="1">
         <v>21.1</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="1">
         <v>20.11</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="1">
         <v>18.350000000000001</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="1">
         <v>20.420000000000002</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="1">
         <v>18.920000000000002</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="1">
         <v>19.739999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="4">
+        <v>70</v>
+      </c>
+      <c r="B18" s="1">
         <v>14.94</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="1">
         <v>13.04</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="1">
         <v>12.19</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="1">
         <v>12.18</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="1">
         <v>11.69</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="1">
         <v>12.32</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="1">
         <v>14.86</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="1">
         <v>12.31</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="1">
         <v>13.54</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="1">
         <v>11.71</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="1">
         <v>18.82</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18" s="1">
         <v>12.55</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="4">
+        <v>105</v>
+      </c>
+      <c r="B19" s="1">
         <v>22.07</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="1">
         <v>22.18</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="1">
         <v>13.7</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="1">
         <v>44.22</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="1">
         <v>28.75</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="1">
         <v>8.76</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="1">
         <v>8.35</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="1">
         <v>9.2200000000000006</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="1">
         <v>12.77</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="1">
         <v>7.74</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="1">
         <v>8.07</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="1">
         <v>8.68</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="4">
+        <v>67</v>
+      </c>
+      <c r="B20" s="1">
         <v>72.94</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="1">
         <v>114.89</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="1">
         <v>103.08</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="1">
         <v>79.37</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="1">
         <v>136.72</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="1">
         <v>68.44</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="1">
         <v>143.08000000000001</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="1">
         <v>52.26</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="1">
         <v>39.590000000000003</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="1">
         <v>127.8</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="1">
         <v>42.56</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="1">
         <v>38.22</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="4">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1">
         <v>30.31</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="1">
         <v>40.36</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="1">
         <v>20.12</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="1">
         <v>20.65</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="1">
         <v>31.11</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="1">
         <v>21.48</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="1">
         <v>29.78</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="1">
         <v>21</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="1">
         <v>21.16</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="1">
         <v>31.95</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="1">
         <v>22.16</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="1">
         <v>23.32</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="4">
+        <v>106</v>
+      </c>
+      <c r="B22" s="1">
         <v>121.39</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="1">
         <v>122.08</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="1">
         <v>119.76</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="1">
         <v>148.47999999999999</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="1">
         <v>138.58000000000001</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="1">
         <v>40.29</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="1">
         <v>45.54</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="1">
         <v>39.299999999999997</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="1">
         <v>36.1</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="1">
         <v>54.15</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="1">
         <v>34.22</v>
       </c>
-      <c r="M22" s="4">
+      <c r="M22" s="1">
         <v>36.159999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="4">
+        <v>65</v>
+      </c>
+      <c r="B23" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="1">
         <v>37.369999999999997</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="1">
         <v>29.16</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="1">
         <v>38.96</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="1">
         <v>36.9</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="1">
         <v>34.97</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="1">
         <v>30.72</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="1">
         <v>30.13</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="1">
         <v>30.2</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="1">
         <v>36.6</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="1">
         <v>28.88</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="1">
         <v>32.1</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="11.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24" s="4">
+        <v>107</v>
+      </c>
+      <c r="B24" s="1">
         <v>61.68</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="1">
         <v>61.8</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="1">
         <v>55.91</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="1">
         <v>65.89</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="1">
         <v>85.32</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="1">
         <v>50.33</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="1">
         <v>48.16</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="1">
         <v>50.08</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="1">
         <v>86.36</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="1">
         <v>79.25</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="1">
         <v>48.59</v>
       </c>
-      <c r="M24" s="4">
+      <c r="M24" s="1">
         <v>69.16</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="4">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1">
         <v>50.85</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="1">
         <v>56.19</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="1">
         <v>58.06</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="1">
         <v>51.47</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="1">
         <v>57.98</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="1">
         <v>106.01</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="1">
         <v>59.12</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="1">
         <v>38.17</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="1">
         <v>36.46</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="1">
         <v>50.87</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="1">
         <v>40.130000000000003</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M25" s="1">
         <v>35.35</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="4">
+        <v>37</v>
+      </c>
+      <c r="B26" s="1">
         <v>35.380000000000003</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="1">
         <v>21.93</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="1">
         <v>21.11</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="1">
         <v>21.49</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="1">
         <v>25.91</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="1">
         <v>30.2</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="1">
         <v>24.04</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="1">
         <v>23.3</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="1">
         <v>23.75</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="1">
         <v>28.47</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="1">
         <v>22.65</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="1">
         <v>23.18</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="4">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1">
         <v>12.24</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="1">
         <v>11.96</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="1">
         <v>11.62</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="1">
         <v>12.29</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="1">
         <v>11.83</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="1">
         <v>11.45</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="1">
         <v>11.67</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="1">
         <v>11.49</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="1">
         <v>11.52</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="1">
         <v>10.93</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="1">
         <v>14.95</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="1">
         <v>14.83</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="4">
+        <v>62</v>
+      </c>
+      <c r="B28" s="1">
         <v>45.87</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="1">
         <v>47.98</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="1">
         <v>46.93</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="1">
         <v>57.94</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="1">
         <v>44.39</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>184</v>
+      <c r="G28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>185</v>
-      </c>
-      <c r="B29" s="4">
+        <v>100</v>
+      </c>
+      <c r="B29" s="1">
         <v>45.1</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="1">
         <v>47.72</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="1">
         <v>40.880000000000003</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="1">
         <v>49.4</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="1">
         <v>65.55</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="1">
         <v>72.930000000000007</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="1">
         <v>75.959999999999994</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="1">
         <v>36.020000000000003</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="1">
         <v>38.340000000000003</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29" s="1">
         <v>40.020000000000003</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="1">
         <v>36.630000000000003</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="1">
         <v>38.979999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>193</v>
-      </c>
-      <c r="B30" s="4">
+        <v>108</v>
+      </c>
+      <c r="B30" s="1">
         <v>65.069999999999993</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="1">
         <v>65.75</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="1">
         <v>154.38</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="1">
         <v>65.260000000000005</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="1">
         <v>30.2</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="1">
         <v>65.09</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="1">
         <v>116.3</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="1">
         <v>65.209999999999994</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="1">
         <v>64.84</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="1">
         <v>112.99</v>
       </c>
-      <c r="L30" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M30" s="4">
+      <c r="L30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M30" s="1">
         <v>64.959999999999994</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="4">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1">
         <v>24.59</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="1">
         <v>24.76</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="1">
         <v>19.05</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="1">
         <v>22.93</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="1">
         <v>17.87</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="1">
         <v>21.65</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="1">
         <v>29.35</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="1">
         <v>21.52</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="1">
         <v>15</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="1">
         <v>24.05</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="1">
         <v>32.5</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M31" s="1">
         <v>12.26</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="4">
+        <v>59</v>
+      </c>
+      <c r="B32" s="1">
         <v>44.39</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="1">
         <v>44.94</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="1">
         <v>40.15</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="1">
         <v>73.31</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="1">
         <v>43.78</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="1">
         <v>30</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="1">
         <v>25.45</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="1">
         <v>23.04</v>
       </c>
-      <c r="J32" s="4">
+      <c r="J32" s="1">
         <v>20.94</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32" s="1">
         <v>23.24</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32" s="1">
         <v>18.71</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="1">
         <v>24.15</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="4">
+        <v>60</v>
+      </c>
+      <c r="B33" s="1">
         <v>14.17</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="1">
         <v>14.58</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="1">
         <v>8.5</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="1">
         <v>14.1</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="1">
         <v>10.86</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="1">
         <v>9.98</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="1">
         <v>9.68</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="1">
         <v>9.24</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="1">
         <v>10.88</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33" s="1">
         <v>10.130000000000001</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="1">
         <v>12.65</v>
       </c>
-      <c r="M33" s="4">
+      <c r="M33" s="1">
         <v>16.190000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" s="4">
+        <v>58</v>
+      </c>
+      <c r="B34" s="1">
         <v>64.88</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="1">
         <v>59.27</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="1">
         <v>65.89</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="1">
         <v>65.760000000000005</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="1">
         <v>65.61</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="1">
         <v>43.23</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="1">
         <v>65.510000000000005</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="1">
         <v>38.869999999999997</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="1">
         <v>38.92</v>
       </c>
-      <c r="K34" s="4">
+      <c r="K34" s="1">
         <v>151.47999999999999</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34" s="1">
         <v>41.31</v>
       </c>
-      <c r="M34" s="4">
+      <c r="M34" s="1">
         <v>38.799999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>186</v>
-      </c>
-      <c r="B35" s="4">
+        <v>101</v>
+      </c>
+      <c r="B35" s="1">
         <v>8.7200000000000006</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="1">
         <v>9.7200000000000006</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="1">
         <v>7.97</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="1">
         <v>8.4</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="1">
         <v>7.98</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="1">
         <v>30.77</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="1">
         <v>9.16</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="1">
         <v>8.99</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="1">
         <v>8.33</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K35" s="1">
         <v>8.32</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="1">
         <v>9.08</v>
       </c>
-      <c r="M35" s="4">
+      <c r="M35" s="1">
         <v>11.26</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="4">
+        <v>52</v>
+      </c>
+      <c r="B36" s="1">
         <v>8.73</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="1">
         <v>8.73</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="1">
         <v>12.58</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="1">
         <v>9.84</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="1">
         <v>11.72</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="1">
         <v>5.97</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="1">
         <v>7.94</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="1">
         <v>4.3</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="1">
         <v>4.16</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="1">
         <v>5.16</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="1">
         <v>5.22</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="1">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="4">
+        <v>42</v>
+      </c>
+      <c r="B37" s="1">
         <v>12.4</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="1">
         <v>12.48</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="1">
         <v>12.8</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="1">
         <v>12.63</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="1">
         <v>13.45</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="1">
         <v>12.46</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="1">
         <v>12.9</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="1">
         <v>12.64</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="1">
         <v>13.13</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37" s="1">
         <v>12.31</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="1">
         <v>13.21</v>
       </c>
-      <c r="M37" s="4">
+      <c r="M37" s="1">
         <v>15.18</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="4">
+        <v>55</v>
+      </c>
+      <c r="B38" s="1">
         <v>141.34</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="1">
         <v>154.03</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="1">
         <v>134.5</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="1">
         <v>141.34</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="1">
         <v>57.26</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="1">
         <v>142.88999999999999</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H38" s="1">
         <v>131.71</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="1">
         <v>157.44</v>
       </c>
-      <c r="J38" s="4">
+      <c r="J38" s="1">
         <v>143.66</v>
       </c>
-      <c r="K38" s="4">
+      <c r="K38" s="1">
         <v>119.55</v>
       </c>
-      <c r="L38" s="4">
+      <c r="L38" s="1">
         <v>92.54</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="1">
         <v>141.56</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="4">
+        <v>49</v>
+      </c>
+      <c r="B39" s="1">
         <v>17.940000000000001</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="1">
         <v>17.27</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="1">
         <v>17.55</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="1">
         <v>17.46</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="1">
         <v>17.79</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="1">
         <v>17.559999999999999</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="1">
         <v>18.04</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="1">
         <v>18.29</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39" s="1">
         <v>17.41</v>
       </c>
-      <c r="K39" s="4">
+      <c r="K39" s="1">
         <v>17.72</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L39" s="1">
         <v>17.510000000000002</v>
       </c>
-      <c r="M39" s="4">
+      <c r="M39" s="1">
         <v>20.04</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B40" s="4">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1">
         <v>15.35</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="1">
         <v>15.57</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="1">
         <v>8.7100000000000009</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="1">
         <v>8.64</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="1">
         <v>9.26</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="1">
         <v>18.34</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H40" s="1">
         <v>15.4</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40" s="1">
         <v>18.579999999999998</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J40" s="1">
         <v>34.18</v>
       </c>
-      <c r="K40" s="4">
+      <c r="K40" s="1">
         <v>32.36</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40" s="1">
         <v>14.5</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M40" s="1">
         <v>40.71</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>194</v>
-      </c>
-      <c r="B41" s="4">
+        <v>109</v>
+      </c>
+      <c r="B41" s="1">
         <v>120.81</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="1">
         <v>121.98</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="1">
         <v>125.07</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="1">
         <v>120.9</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="1">
         <v>124.66</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="1">
         <v>95.96</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H41" s="1">
         <v>125.04</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I41" s="1">
         <v>91.57</v>
       </c>
-      <c r="J41" s="4">
+      <c r="J41" s="1">
         <v>77.95</v>
       </c>
-      <c r="K41" s="4">
+      <c r="K41" s="1">
         <v>124.4</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="1">
         <v>74.02</v>
       </c>
-      <c r="M41" s="4">
+      <c r="M41" s="1">
         <v>69.53</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
         <v>192.36</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="1">
         <v>192.36</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="1">
         <v>167.62</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="1">
         <v>192.36</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="1">
         <v>172.8</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="1">
         <v>190.14</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H42" s="1">
         <v>185.05</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42" s="1">
         <v>195.03</v>
       </c>
-      <c r="J42" s="4">
+      <c r="J42" s="1">
         <v>104.39</v>
       </c>
-      <c r="K42" s="4">
+      <c r="K42" s="1">
         <v>196.97</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="1">
         <v>12.8</v>
       </c>
-      <c r="M42" s="4">
+      <c r="M42" s="1">
         <v>12.7</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="4">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1">
         <v>35.99</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="1">
         <v>35.97</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="1">
         <v>37.340000000000003</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="1">
         <v>67.5</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="1">
         <v>37.549999999999997</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="1">
         <v>45.32</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="1">
         <v>35.549999999999997</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="1">
         <v>39.32</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="1">
         <v>40.22</v>
       </c>
-      <c r="K43" s="4">
+      <c r="K43" s="1">
         <v>56.03</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="1">
         <v>37.020000000000003</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="1">
         <v>56.62</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
         <v>11.77</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="1">
         <v>5.82</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="1">
         <v>3.81</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="1">
         <v>4.05</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="1">
         <v>5.17</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="1">
         <v>5.75</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44" s="1">
         <v>4.2300000000000004</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="1">
         <v>5.55</v>
       </c>
-      <c r="J44" s="4">
+      <c r="J44" s="1">
         <v>4.13</v>
       </c>
-      <c r="K44" s="4">
+      <c r="K44" s="1">
         <v>4.17</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44" s="1">
         <v>4.88</v>
       </c>
-      <c r="M44" s="4">
+      <c r="M44" s="1">
         <v>4.3600000000000003</v>
       </c>
     </row>
@@ -6256,111 +4934,111 @@
   <sheetFormatPr defaultColWidth="12.26953125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>201</v>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2">
         <v>15.714183071447</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>18.912346468482902</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>13.872132464167899</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>12.5407579384868</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>15.4462767237981</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="2">
         <v>10.812995542649899</v>
       </c>
       <c r="H4" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -6384,166 +5062,166 @@
   <sheetFormatPr defaultColWidth="12.26953125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>201</v>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2">
         <v>15.714183071447</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>18.912346468482902</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>13.872132464167899</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>12.5407579384868</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>15.4462767237981</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="2">
         <v>10.812995542649899</v>
       </c>
       <c r="H4" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>204</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>208</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
